--- a/Incunest_v15/Hardware/BOM/Bill of Materials-in3ator(Main).xlsx
+++ b/Incunest_v15/Hardware/BOM/Bill of Materials-in3ator(Main).xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carloshm/personal-projects/IncuNest-WorkWi-Chips/Incunest_v15/Hardware/BOM/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2941E1C5-0009-CD47-A3A0-5D7DC92C62F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="4420" yWindow="660" windowWidth="16380" windowHeight="8200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Bill of Materials-in3ator(Main)" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Bill of Materials-in3ator(Main)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="Print_Titles" vbProcedure="false">'Bill of Materials-in3ator(Main)'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Bill of Materials-in3ator(Main)'!$1:$1</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -25,13 +30,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="208">
   <si>
-    <t xml:space="preserve">Comment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Designator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Footprint</t>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>Designator</t>
+  </si>
+  <si>
+    <t>Footprint</t>
   </si>
   <si>
     <r>
@@ -39,704 +44,678 @@
         <sz val="11"/>
         <color rgb="FFAFABAB"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
-      <t xml:space="preserve">JLCPCB Part #</t>
+      <t>JLCPCB Part #</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FFAFABAB"/>
         <rFont val="宋体"/>
-        <family val="0"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">（</t>
+      <t>（</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FFAFABAB"/>
         <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
-      <t xml:space="preserve">optional</t>
+      <t>optional</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FFAFABAB"/>
         <rFont val="宋体"/>
-        <family val="0"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">）</t>
+      <t>）</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">CUI CMT-1285C-035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUZ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C252915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100nF 0402 X7R 50V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1, C5, C6, C8, C11, C14, C16, C30, C34, C38, C41, C42, C46, C50, C59, C60, C62, C63, C64, C70, C73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C77020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10uF 0402 X5R 10V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2, C3, C21, C22, C23, C24, C25, C26, C27, C28, C29, C35, C36, C37, C49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C77000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1uF 0402 X5R 25V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C4, C7, C15, C17, C52, C53, C61, C65, C66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C77009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18pF 0402 X5R 50V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C12, C43, C54, C58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C33149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10uF 0603 X5R 25V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C31, C32, C39, C40, C44, C45, C67, C68, C69, C71, C72, C77, C78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C91606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10nF 0402 X7R 50V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C60133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2uF 0402 X5R 25V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C56, C57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C77002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47nF 0402 X7R 50V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C74, C76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C272875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1nF 0402 X7R 50V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C106205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LESD5D5.0CT1G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D1, D3, D30, D39, D40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C383211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESDA6V1-5SC6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C6650</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESD9B3.3ST5G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D4, D5, D7, D10, D11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C96512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMBJ13A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C404130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMSZ5231BT1G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2759896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1N5711WS-7-F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D9, D34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C151442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FSV1550V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D12, D35, D36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C668953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VLMB1300-GS08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C435849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAV99W-7-F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D28, D29, D31, D32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C93035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAT54C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C181200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Degson 2EDGK-5.08-02P-14-00AH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J1, J15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C8445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samtec SLW-103-01-T-D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C492420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PJ-3059-B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2884976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B4B-XH-A(LF)(SN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C144395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62201021121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C7501289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TE Connectivity 1734366-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C32896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WJ15EDGVC-3.81-2P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C8396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KF2EDGVC-5.08-4P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C441388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-5747706-0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C189689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1217AS-H-3R3N=P3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L1, L2, L3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C514864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DFE201612E-1R0M=P2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C521238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPD90P03P404ATMA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q1, Q5, Q7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C148439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRLR7843TRPBF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C21988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRLML6244TRPBF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q3, Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C143946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSS138W-7-F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q6, Q8, Q9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C24553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.002R 1206 0.5W 1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R1, R52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C601094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10k 0402 0.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R2, R9, R11, R19, R21, R23, R25, R29, R30, R31, R33, R34, R35, R37, R38, R39, R41, R42, R46, R57, R59, R71, R72, R73, R83, R84, R87, R91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C190095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1k 0402 1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R4, R6, R7, R10, R12, R13, R20, R26, R43, R44, R49, R62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C106235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1R 1206 0.5W 1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R5, R51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C601090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100k 0402 0.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R14, R80, R81, R86, R94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C60491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0R 0402 1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R15, R47, R53, R78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C60485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100R 0402 0.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R16, R17, R18, R88, R90, R95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C106233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.082R 1206 0.5W 1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C705560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0R 1206 0.5W 1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C108081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51k 0402 0.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R32, R40, R75, R82</t>
+    <t>CUI CMT-1285C-035</t>
+  </si>
+  <si>
+    <t>BUZ1</t>
+  </si>
+  <si>
+    <t>C252915</t>
+  </si>
+  <si>
+    <t>100nF 0402 X7R 50V</t>
+  </si>
+  <si>
+    <t>C1, C5, C6, C8, C11, C14, C16, C30, C34, C38, C41, C42, C46, C50, C59, C60, C62, C63, C64, C70, C73</t>
+  </si>
+  <si>
+    <t>C77020</t>
+  </si>
+  <si>
+    <t>10uF 0402 X5R 10V</t>
+  </si>
+  <si>
+    <t>C2, C3, C21, C22, C23, C24, C25, C26, C27, C28, C29, C35, C36, C37, C49</t>
+  </si>
+  <si>
+    <t>C77000</t>
+  </si>
+  <si>
+    <t>1uF 0402 X5R 25V</t>
+  </si>
+  <si>
+    <t>C4, C7, C15, C17, C52, C53, C61, C65, C66</t>
+  </si>
+  <si>
+    <t>C77009</t>
+  </si>
+  <si>
+    <t>18pF 0402 X5R 50V</t>
+  </si>
+  <si>
+    <t>C12, C43, C54, C58</t>
+  </si>
+  <si>
+    <t>C33149</t>
+  </si>
+  <si>
+    <t>10uF 0603 X5R 25V</t>
+  </si>
+  <si>
+    <t>C31, C32, C39, C40, C44, C45, C67, C68, C69, C71, C72, C77, C78</t>
+  </si>
+  <si>
+    <t>C91606</t>
+  </si>
+  <si>
+    <t>10nF 0402 X7R 50V</t>
+  </si>
+  <si>
+    <t>C55</t>
+  </si>
+  <si>
+    <t>C60133</t>
+  </si>
+  <si>
+    <t>2.2uF 0402 X5R 25V</t>
+  </si>
+  <si>
+    <t>C56, C57</t>
+  </si>
+  <si>
+    <t>C77002</t>
+  </si>
+  <si>
+    <t>47nF 0402 X7R 50V</t>
+  </si>
+  <si>
+    <t>C74, C76</t>
+  </si>
+  <si>
+    <t>C272875</t>
+  </si>
+  <si>
+    <t>1nF 0402 X7R 50V</t>
+  </si>
+  <si>
+    <t>C75</t>
+  </si>
+  <si>
+    <t>C106205</t>
+  </si>
+  <si>
+    <t>LESD5D5.0CT1G</t>
+  </si>
+  <si>
+    <t>D1, D3, D30, D39, D40</t>
+  </si>
+  <si>
+    <t>C383211</t>
+  </si>
+  <si>
+    <t>ESDA6V1-5SC6</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>C6650</t>
+  </si>
+  <si>
+    <t>ESD9B3.3ST5G</t>
+  </si>
+  <si>
+    <t>D4, D5, D7, D10, D11</t>
+  </si>
+  <si>
+    <t>C96512</t>
+  </si>
+  <si>
+    <t>SMBJ13A</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>C404130</t>
+  </si>
+  <si>
+    <t>MMSZ5231BT1G</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>C2759896</t>
+  </si>
+  <si>
+    <t>1N5711WS-7-F</t>
+  </si>
+  <si>
+    <t>D9, D34</t>
+  </si>
+  <si>
+    <t>C151442</t>
+  </si>
+  <si>
+    <t>FSV1550V</t>
+  </si>
+  <si>
+    <t>D12, D35, D36</t>
+  </si>
+  <si>
+    <t>C668953</t>
+  </si>
+  <si>
+    <t>VLMB1300-GS08</t>
+  </si>
+  <si>
+    <t>D27</t>
+  </si>
+  <si>
+    <t>C435849</t>
+  </si>
+  <si>
+    <t>BAV99W-7-F</t>
+  </si>
+  <si>
+    <t>D28, D29, D31, D32</t>
+  </si>
+  <si>
+    <t>C93035</t>
+  </si>
+  <si>
+    <t>BAT54C</t>
+  </si>
+  <si>
+    <t>D33</t>
+  </si>
+  <si>
+    <t>C181200</t>
+  </si>
+  <si>
+    <t>Degson 2EDGK-5.08-02P-14-00AH</t>
+  </si>
+  <si>
+    <t>J1, J15</t>
+  </si>
+  <si>
+    <t>C8445</t>
+  </si>
+  <si>
+    <t>Samtec SLW-103-01-T-D</t>
+  </si>
+  <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>C492420</t>
+  </si>
+  <si>
+    <t>PJ-3059-B</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>C2884976</t>
+  </si>
+  <si>
+    <t>B4B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>J5</t>
+  </si>
+  <si>
+    <t>C144395</t>
+  </si>
+  <si>
+    <t>62201021121</t>
+  </si>
+  <si>
+    <t>J6</t>
+  </si>
+  <si>
+    <t>C7501289</t>
+  </si>
+  <si>
+    <t>TE Connectivity 1734366-3</t>
+  </si>
+  <si>
+    <t>J7</t>
+  </si>
+  <si>
+    <t>C32896</t>
+  </si>
+  <si>
+    <t>WJ15EDGVC-3.81-2P</t>
+  </si>
+  <si>
+    <t>J8</t>
+  </si>
+  <si>
+    <t>C8396</t>
+  </si>
+  <si>
+    <t>KF2EDGVC-5.08-4P</t>
+  </si>
+  <si>
+    <t>J9</t>
+  </si>
+  <si>
+    <t>C441388</t>
+  </si>
+  <si>
+    <t>2-5747706-0</t>
+  </si>
+  <si>
+    <t>J14</t>
+  </si>
+  <si>
+    <t>C189689</t>
+  </si>
+  <si>
+    <t>1217AS-H-3R3N=P3</t>
+  </si>
+  <si>
+    <t>L1, L2, L3</t>
+  </si>
+  <si>
+    <t>C514864</t>
+  </si>
+  <si>
+    <t>DFE201612E-1R0M=P2</t>
+  </si>
+  <si>
+    <t>L5</t>
+  </si>
+  <si>
+    <t>C521238</t>
+  </si>
+  <si>
+    <t>IPD90P03P404ATMA1</t>
+  </si>
+  <si>
+    <t>Q1, Q5, Q7</t>
+  </si>
+  <si>
+    <t>C148439</t>
+  </si>
+  <si>
+    <t>IRLR7843TRPBF</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>C21988</t>
+  </si>
+  <si>
+    <t>IRLML6244TRPBF</t>
+  </si>
+  <si>
+    <t>Q3, Q4</t>
+  </si>
+  <si>
+    <t>C143946</t>
+  </si>
+  <si>
+    <t>BSS138W-7-F</t>
+  </si>
+  <si>
+    <t>Q6, Q8, Q9</t>
+  </si>
+  <si>
+    <t>C24553</t>
+  </si>
+  <si>
+    <t>0.002R 1206 0.5W 1%</t>
+  </si>
+  <si>
+    <t>R1, R52</t>
+  </si>
+  <si>
+    <t>C601094</t>
+  </si>
+  <si>
+    <t>10k 0402 0.1%</t>
+  </si>
+  <si>
+    <t>R2, R9, R11, R19, R21, R23, R25, R29, R30, R31, R33, R34, R35, R37, R38, R39, R41, R42, R46, R57, R59, R71, R72, R73, R83, R84, R87, R91</t>
+  </si>
+  <si>
+    <t>C190095</t>
+  </si>
+  <si>
+    <t>1k 0402 1%</t>
+  </si>
+  <si>
+    <t>R4, R6, R7, R10, R12, R13, R20, R26, R43, R44, R49, R62</t>
+  </si>
+  <si>
+    <t>C106235</t>
+  </si>
+  <si>
+    <t>0.1R 1206 0.5W 1%</t>
+  </si>
+  <si>
+    <t>R5, R51</t>
+  </si>
+  <si>
+    <t>C601090</t>
+  </si>
+  <si>
+    <t>100k 0402 0.1%</t>
+  </si>
+  <si>
+    <t>R14, R80, R81, R86, R94</t>
+  </si>
+  <si>
+    <t>C60491</t>
+  </si>
+  <si>
+    <t>0R 0402 1%</t>
+  </si>
+  <si>
+    <t>R15, R47, R53, R78</t>
+  </si>
+  <si>
+    <t>C60485</t>
+  </si>
+  <si>
+    <t>100R 0402 0.1%</t>
+  </si>
+  <si>
+    <t>R16, R17, R18, R88, R90, R95</t>
+  </si>
+  <si>
+    <t>C106233</t>
+  </si>
+  <si>
+    <t>0.082R 1206 0.5W 1%</t>
+  </si>
+  <si>
+    <t>R22</t>
+  </si>
+  <si>
+    <t>C705560</t>
+  </si>
+  <si>
+    <t>0R 1206 0.5W 1%</t>
+  </si>
+  <si>
+    <t>R28</t>
+  </si>
+  <si>
+    <t>C108081</t>
+  </si>
+  <si>
+    <t>51k 0402 0.1%</t>
+  </si>
+  <si>
+    <t>R32, R40, R75, R82</t>
   </si>
   <si>
     <t xml:space="preserve">C147794 </t>
   </si>
   <si>
-    <t xml:space="preserve">17k4 0402 0.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R36, R92, R99</t>
+    <t>17k4 0402 0.1%</t>
+  </si>
+  <si>
+    <t>R36, R92, R99</t>
   </si>
   <si>
     <t xml:space="preserve">C517755 </t>
   </si>
   <si>
-    <t xml:space="preserve">73k2 0402 1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R45, R76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C185398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56k 0402 0.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C114756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130Ohm 0402 1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R60, R61, R65, R66, R67, R68, R69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C413066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2k26 0402 0.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R77</t>
+    <t>73k2 0402 1%</t>
+  </si>
+  <si>
+    <t>R45, R76</t>
+  </si>
+  <si>
+    <t>C185398</t>
+  </si>
+  <si>
+    <t>56k 0402 0.1%</t>
+  </si>
+  <si>
+    <t>R50</t>
+  </si>
+  <si>
+    <t>C114756</t>
+  </si>
+  <si>
+    <t>130Ohm 0402 1%</t>
+  </si>
+  <si>
+    <t>R60, R61, R65, R66, R67, R68, R69</t>
+  </si>
+  <si>
+    <t>C413066</t>
+  </si>
+  <si>
+    <t>2k26 0402 0.1%</t>
+  </si>
+  <si>
+    <t>R77</t>
   </si>
   <si>
     <t xml:space="preserve">C270627 </t>
   </si>
   <si>
-    <t xml:space="preserve">0.005R 1206 0.5W 0.5% 100ppm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C723507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127k 0402 0.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C138061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XKB7070-Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SW2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C318863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESP32-S3-WROOM-1-N8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2913198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simcom SIM800C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C69119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eSIM MFF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C5122390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INA3221AIRGVR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U4, U9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C181255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LTV-356T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U5, U7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C125117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPS563231DRLR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U6, U10, U11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C779412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TYPE-C 16PLC-H10.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U12, U13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C3151747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WS2812B-B/T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2761795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPX3819M5-L-3-3/TR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U16, U22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C9055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFE4490RHAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2651608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LM2903BIDR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2869804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SN74LVC1G3157DCKR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C10426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BQ34110PWR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BQ25792RQMR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2862876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABM3-8.000MHZ-D2Y-T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C144380</t>
+    <t>0.005R 1206 0.5W 0.5% 100ppm</t>
+  </si>
+  <si>
+    <t>R89</t>
+  </si>
+  <si>
+    <t>C723507</t>
+  </si>
+  <si>
+    <t>127k 0402 0.1%</t>
+  </si>
+  <si>
+    <t>R93</t>
+  </si>
+  <si>
+    <t>C138061</t>
+  </si>
+  <si>
+    <t>XKB7070-Z</t>
+  </si>
+  <si>
+    <t>SW2</t>
+  </si>
+  <si>
+    <t>C318863</t>
+  </si>
+  <si>
+    <t>ESP32-S3-WROOM-1-N8</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>C2913198</t>
+  </si>
+  <si>
+    <t>Simcom SIM800C</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>C69119</t>
+  </si>
+  <si>
+    <t>eSIM MFF2</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>C5122390</t>
+  </si>
+  <si>
+    <t>INA3221AIRGVR</t>
+  </si>
+  <si>
+    <t>U4, U9</t>
+  </si>
+  <si>
+    <t>C181255</t>
+  </si>
+  <si>
+    <t>LTV-356T</t>
+  </si>
+  <si>
+    <t>U5, U7</t>
+  </si>
+  <si>
+    <t>C125117</t>
+  </si>
+  <si>
+    <t>TPS563231DRLR</t>
+  </si>
+  <si>
+    <t>U6, U10, U11</t>
+  </si>
+  <si>
+    <t>C779412</t>
+  </si>
+  <si>
+    <t>TYPE-C 16PLC-H10.0</t>
+  </si>
+  <si>
+    <t>U12, U13</t>
+  </si>
+  <si>
+    <t>C3151747</t>
+  </si>
+  <si>
+    <t>WS2812B-B/T</t>
+  </si>
+  <si>
+    <t>U14</t>
+  </si>
+  <si>
+    <t>C2761795</t>
+  </si>
+  <si>
+    <t>SPX3819M5-L-3-3/TR</t>
+  </si>
+  <si>
+    <t>U16, U22</t>
+  </si>
+  <si>
+    <t>C9055</t>
+  </si>
+  <si>
+    <t>AFE4490RHAR</t>
+  </si>
+  <si>
+    <t>U17</t>
+  </si>
+  <si>
+    <t>C2651608</t>
+  </si>
+  <si>
+    <t>LM2903BIDR</t>
+  </si>
+  <si>
+    <t>U19</t>
+  </si>
+  <si>
+    <t>C2869804</t>
+  </si>
+  <si>
+    <t>SN74LVC1G3157DCKR</t>
+  </si>
+  <si>
+    <t>U20</t>
+  </si>
+  <si>
+    <t>C10426</t>
+  </si>
+  <si>
+    <t>BQ34110PWR</t>
+  </si>
+  <si>
+    <t>U21</t>
+  </si>
+  <si>
+    <t>C2877075</t>
+  </si>
+  <si>
+    <t>BQ25792RQMR</t>
+  </si>
+  <si>
+    <t>U23</t>
+  </si>
+  <si>
+    <t>C2862876</t>
+  </si>
+  <si>
+    <t>ABM3-8.000MHZ-D2Y-T</t>
+  </si>
+  <si>
+    <t>Y1</t>
+  </si>
+  <si>
+    <t>C144380</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Tahoma"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFAFABAB"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFAFABAB"/>
       <name val="宋体"/>
-      <family val="0"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -749,94 +728,75 @@
     </fill>
   </fills>
   <borders count="4">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
-      <right style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -895,24 +855,352 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D69"/>
-  <sheetFormatPr defaultColWidth="8.48046875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.3984375" defaultRowHeight="13"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="20.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.8"/>
+    <col min="1" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="16.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" ht="16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -926,952 +1214,952 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="4">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="4">
         <v>21</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="4">
         <v>15</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="4">
         <v>9</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="4">
         <v>4</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="4">
         <v>13</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="4">
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="4">
         <v>2</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="4">
         <v>2</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="4">
         <v>1</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="4">
         <v>5</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="4">
         <v>1</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:4">
       <c r="A14" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="4">
         <v>5</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="4">
         <v>1</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:4">
       <c r="A16" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="4">
         <v>1</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:4">
       <c r="A17" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="4">
         <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:4">
       <c r="A18" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="4">
         <v>3</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:4">
       <c r="A19" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="4">
         <v>1</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:4">
       <c r="A20" s="3" t="s">
         <v>58</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="4">
         <v>4</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:4">
       <c r="A21" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="4">
         <v>1</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:4">
       <c r="A22" s="3" t="s">
         <v>64</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="4">
         <v>2</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:4">
       <c r="A23" s="3" t="s">
         <v>67</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="4">
         <v>1</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:4">
       <c r="A24" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="4">
         <v>1</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:4">
       <c r="A25" s="3" t="s">
         <v>73</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="4">
         <v>1</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:4">
       <c r="A26" s="3" t="s">
         <v>76</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="4">
         <v>1</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:4">
       <c r="A27" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C27" s="4" t="n">
+      <c r="C27" s="4">
         <v>1</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:4">
       <c r="A28" s="3" t="s">
         <v>82</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="4">
         <v>1</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:4">
       <c r="A29" s="3" t="s">
         <v>85</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" s="4">
         <v>1</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:4">
       <c r="A30" s="3" t="s">
         <v>88</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="4">
         <v>1</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:4">
       <c r="A31" s="3" t="s">
         <v>91</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="4">
         <v>3</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:4">
       <c r="A32" s="3" t="s">
         <v>94</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="4">
         <v>1</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:4">
       <c r="A33" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="4">
         <v>3</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:4">
       <c r="A34" s="3" t="s">
         <v>100</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="4">
         <v>1</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
         <v>103</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="4" t="n">
+      <c r="C35" s="4">
         <v>2</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
         <v>106</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="4">
         <v>3</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
         <v>109</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="4">
         <v>2</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
         <v>112</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C38" s="4" t="n">
+      <c r="C38" s="4">
         <v>28</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
         <v>115</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C39" s="4" t="n">
+      <c r="C39" s="4">
         <v>12</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
         <v>118</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C40" s="4" t="n">
+      <c r="C40" s="4">
         <v>2</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
         <v>121</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C41" s="4" t="n">
+      <c r="C41" s="4">
         <v>5</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:4">
       <c r="A42" s="3" t="s">
         <v>124</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C42" s="4" t="n">
+      <c r="C42" s="4">
         <v>4</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:4">
       <c r="A43" s="3" t="s">
         <v>127</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C43" s="4" t="n">
+      <c r="C43" s="4">
         <v>6</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C44" s="4" t="n">
+      <c r="C44" s="4">
         <v>1</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="1:4">
       <c r="A45" s="3" t="s">
         <v>133</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C45" s="4" t="n">
+      <c r="C45" s="4">
         <v>1</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="1:4" ht="14">
       <c r="A46" s="3" t="s">
         <v>136</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C46" s="4" t="n">
+      <c r="C46" s="4">
         <v>4</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="1:4" ht="14">
       <c r="A47" s="3" t="s">
         <v>139</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C47" s="4" t="n">
+      <c r="C47" s="4">
         <v>3</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="1:4">
       <c r="A48" s="3" t="s">
         <v>142</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C48" s="4" t="n">
+      <c r="C48" s="4">
         <v>2</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="1:4">
       <c r="A49" s="3" t="s">
         <v>145</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C49" s="4" t="n">
+      <c r="C49" s="4">
         <v>1</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="1:4">
       <c r="A50" s="3" t="s">
         <v>148</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C50" s="4" t="n">
+      <c r="C50" s="4">
         <v>7</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:4" ht="14">
       <c r="A51" s="3" t="s">
         <v>151</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C51" s="4" t="n">
+      <c r="C51" s="4">
         <v>1</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="1:4">
       <c r="A52" s="3" t="s">
         <v>154</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C52" s="4" t="n">
+      <c r="C52" s="4">
         <v>1</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="1:4">
       <c r="A53" s="3" t="s">
         <v>157</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C53" s="4" t="n">
+      <c r="C53" s="4">
         <v>1</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="1:4">
       <c r="A54" s="3" t="s">
         <v>160</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C54" s="4" t="n">
+      <c r="C54" s="4">
         <v>1</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="1:4">
       <c r="A55" s="3" t="s">
         <v>163</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C55" s="4" t="n">
+      <c r="C55" s="4">
         <v>1</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="1:4">
       <c r="A56" s="3" t="s">
         <v>166</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C56" s="4" t="n">
+      <c r="C56" s="4">
         <v>1</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="1:4">
       <c r="A57" s="3" t="s">
         <v>169</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C57" s="4" t="n">
+      <c r="C57" s="4">
         <v>1</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="1:4">
       <c r="A58" s="3" t="s">
         <v>172</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C58" s="4" t="n">
+      <c r="C58" s="4">
         <v>2</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="1:4">
       <c r="A59" s="3" t="s">
         <v>175</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C59" s="4" t="n">
+      <c r="C59" s="4">
         <v>2</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="1:4">
       <c r="A60" s="3" t="s">
         <v>178</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C60" s="4" t="n">
+      <c r="C60" s="4">
         <v>3</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" spans="1:4">
       <c r="A61" s="3" t="s">
         <v>181</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C61" s="4" t="n">
+      <c r="C61" s="4">
         <v>2</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" spans="1:4">
       <c r="A62" s="3" t="s">
         <v>184</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="C62" s="4" t="n">
+      <c r="C62" s="4">
         <v>1</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" spans="1:4">
       <c r="A63" s="3" t="s">
         <v>187</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C63" s="4" t="n">
+      <c r="C63" s="4">
         <v>2</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" spans="1:4">
       <c r="A64" s="3" t="s">
         <v>190</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C64" s="4" t="n">
+      <c r="C64" s="4">
         <v>1</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" spans="1:4">
       <c r="A65" s="3" t="s">
         <v>193</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C65" s="4" t="n">
+      <c r="C65" s="4">
         <v>1</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" spans="1:4">
       <c r="A66" s="3" t="s">
         <v>196</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C66" s="4" t="n">
+      <c r="C66" s="4">
         <v>1</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" spans="1:4">
       <c r="A67" s="3" t="s">
         <v>199</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C67" s="4" t="n">
+      <c r="C67" s="4">
         <v>1</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" spans="1:4">
       <c r="A68" s="3" t="s">
         <v>202</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C68" s="4" t="n">
+      <c r="C68" s="4">
         <v>1</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" spans="1:4">
       <c r="A69" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C69" s="4" t="n">
+      <c r="C69" s="4">
         <v>1</v>
       </c>
       <c r="D69" s="4" t="s">
@@ -1879,12 +2167,7 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>